--- a/.schema/MHR_USER.xlsx
+++ b/.schema/MHR_USER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9F422A-4C4C-4BA4-92BA-3CBEC647DA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70037582-029D-40D7-A45B-AC4A3481BED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43200" yWindow="0" windowWidth="14400" windowHeight="7800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_USER" sheetId="1" r:id="rId1"/>
@@ -120,9 +120,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>64717593f995289f5c64f4abe1265ef7e1b4d6a9f5b3b1062eeef3ec7914f7eaeb4058bb9b3a89cc20e8f997465d37a7be3fde1344a3bcc83ad826a8828e4693</t>
-  </si>
-  <si>
     <t>社長</t>
     <rPh sb="0" eb="2">
       <t>シャチョウ</t>
@@ -465,6 +462,9 @@
       <t>イッパン</t>
     </rPh>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>$argon2id$v=19$m=65536,t=3,p=1$XIsqva5G0L/mdn0MhKO15Q$Eo+HkfrlrM4zTllpmHA3un5s1k9WcWNTRBl0ulHLWwQ</t>
   </si>
 </sst>
 </file>
@@ -901,20 +901,20 @@
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="5">
         <f t="shared" ref="H2:H10" ca="1" si="0">NOW()</f>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="5">
         <f t="shared" ref="J2:J10" ca="1" si="1">NOW()</f>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K2" s="2">
         <v>0</v>
@@ -935,20 +935,20 @@
         <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
       </c>
       <c r="J3" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K3" s="2">
         <v>0</v>
@@ -969,20 +969,20 @@
         <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
       <c r="J4" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K4" s="2">
         <v>0</v>
@@ -1003,20 +1003,20 @@
         <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
@@ -1037,20 +1037,20 @@
         <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
       <c r="J6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K6" s="2">
         <v>0</v>
@@ -1071,20 +1071,20 @@
         <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
       </c>
       <c r="J7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K7" s="2">
         <v>0</v>
@@ -1105,20 +1105,20 @@
         <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
       </c>
       <c r="J8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K8" s="2">
         <v>0</v>
@@ -1139,20 +1139,20 @@
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K9" s="2">
         <v>0</v>
@@ -1173,20 +1173,20 @@
         <v>13</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
       </c>
       <c r="J10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K10" s="2">
         <v>0</v>
@@ -1207,20 +1207,20 @@
         <v>13</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="5">
         <f t="shared" ref="H11:H74" ca="1" si="3">NOW()</f>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="5">
         <f t="shared" ref="J11:J74" ca="1" si="4">NOW()</f>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K11" s="2">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
@@ -1241,20 +1241,20 @@
         <v>13</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
       </c>
       <c r="J12" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>22</v>
@@ -1275,20 +1275,20 @@
         <v>13</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
       </c>
       <c r="J13" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -1300,29 +1300,29 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
       </c>
       <c r="J14" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -1334,29 +1334,29 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
@@ -1368,29 +1368,29 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
       </c>
       <c r="J16" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K16" s="2">
         <v>0</v>
@@ -1402,29 +1402,29 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I17" s="2">
         <v>0</v>
       </c>
       <c r="J17" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K17" s="2">
         <v>0</v>
@@ -1436,29 +1436,29 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I18" s="2">
         <v>0</v>
       </c>
       <c r="J18" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K18" s="2">
         <v>0</v>
@@ -1470,29 +1470,29 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
       </c>
       <c r="J19" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K19" s="2">
         <v>0</v>
@@ -1504,29 +1504,29 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
       </c>
       <c r="J20" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K20" s="2">
         <v>0</v>
@@ -1538,29 +1538,29 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I21" s="2">
         <v>0</v>
       </c>
       <c r="J21" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K21" s="2">
         <v>0</v>
@@ -1572,29 +1572,29 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
       </c>
       <c r="J22" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K22" s="2">
         <v>0</v>
@@ -1606,29 +1606,29 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
       </c>
       <c r="J23" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K23" s="2">
         <v>0</v>
@@ -1640,29 +1640,29 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
@@ -1674,29 +1674,29 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
@@ -1708,29 +1708,29 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
       </c>
       <c r="J26" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K26" s="2">
         <v>0</v>
@@ -1742,29 +1742,29 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K27" s="2">
         <v>0</v>
@@ -1776,29 +1776,29 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I28" s="2">
         <v>0</v>
       </c>
       <c r="J28" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K28" s="2">
         <v>0</v>
@@ -1810,29 +1810,29 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
       </c>
       <c r="J29" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K29" s="2">
         <v>0</v>
@@ -1844,29 +1844,29 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
       </c>
       <c r="J30" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K30" s="2">
         <v>0</v>
@@ -1878,29 +1878,29 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
       </c>
       <c r="J31" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K31" s="2">
         <v>0</v>
@@ -1912,29 +1912,29 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
       </c>
       <c r="J32" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K32" s="2">
         <v>0</v>
@@ -1946,29 +1946,29 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I33" s="2">
         <v>0</v>
       </c>
       <c r="J33" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K33" s="2">
         <v>0</v>
@@ -1980,29 +1980,29 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
       </c>
       <c r="J34" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K34" s="2">
         <v>0</v>
@@ -2014,29 +2014,29 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
       </c>
       <c r="J35" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K35" s="2">
         <v>0</v>
@@ -2048,29 +2048,29 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I36" s="2">
         <v>0</v>
       </c>
       <c r="J36" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K36" s="2">
         <v>0</v>
@@ -2082,29 +2082,29 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I37" s="2">
         <v>0</v>
       </c>
       <c r="J37" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K37" s="2">
         <v>0</v>
@@ -2116,29 +2116,29 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I38" s="2">
         <v>0</v>
       </c>
       <c r="J38" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K38" s="2">
         <v>0</v>
@@ -2150,29 +2150,29 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I39" s="2">
         <v>0</v>
       </c>
       <c r="J39" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K39" s="2">
         <v>0</v>
@@ -2184,29 +2184,29 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I40" s="2">
         <v>0</v>
       </c>
       <c r="J40" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K40" s="2">
         <v>0</v>
@@ -2218,29 +2218,29 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I41" s="2">
         <v>0</v>
       </c>
       <c r="J41" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K41" s="2">
         <v>0</v>
@@ -2252,29 +2252,29 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I42" s="2">
         <v>0</v>
       </c>
       <c r="J42" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K42" s="2">
         <v>0</v>
@@ -2286,29 +2286,29 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I43" s="2">
         <v>0</v>
       </c>
       <c r="J43" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K43" s="2">
         <v>0</v>
@@ -2320,29 +2320,29 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I44" s="2">
         <v>0</v>
       </c>
       <c r="J44" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K44" s="2">
         <v>0</v>
@@ -2354,29 +2354,29 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I45" s="2">
         <v>0</v>
       </c>
       <c r="J45" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K45" s="2">
         <v>0</v>
@@ -2388,29 +2388,29 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I46" s="2">
         <v>0</v>
       </c>
       <c r="J46" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K46" s="2">
         <v>0</v>
@@ -2422,29 +2422,29 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I47" s="2">
         <v>0</v>
       </c>
       <c r="J47" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K47" s="2">
         <v>0</v>
@@ -2456,29 +2456,29 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I48" s="2">
         <v>0</v>
       </c>
       <c r="J48" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K48" s="2">
         <v>0</v>
@@ -2490,29 +2490,29 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I49" s="2">
         <v>0</v>
       </c>
       <c r="J49" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K49" s="2">
         <v>0</v>
@@ -2524,29 +2524,29 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I50" s="2">
         <v>0</v>
       </c>
       <c r="J50" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K50" s="2">
         <v>0</v>
@@ -2558,29 +2558,29 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I51" s="2">
         <v>0</v>
       </c>
       <c r="J51" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K51" s="2">
         <v>0</v>
@@ -2592,29 +2592,29 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I52" s="2">
         <v>0</v>
       </c>
       <c r="J52" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K52" s="2">
         <v>0</v>
@@ -2626,29 +2626,29 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I53" s="2">
         <v>0</v>
       </c>
       <c r="J53" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K53" s="2">
         <v>0</v>
@@ -2660,29 +2660,29 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I54" s="2">
         <v>0</v>
       </c>
       <c r="J54" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K54" s="2">
         <v>0</v>
@@ -2694,29 +2694,29 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I55" s="2">
         <v>0</v>
       </c>
       <c r="J55" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K55" s="2">
         <v>0</v>
@@ -2728,29 +2728,29 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I56" s="2">
         <v>0</v>
       </c>
       <c r="J56" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K56" s="2">
         <v>0</v>
@@ -2762,29 +2762,29 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I57" s="2">
         <v>0</v>
       </c>
       <c r="J57" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K57" s="2">
         <v>0</v>
@@ -2796,29 +2796,29 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I58" s="2">
         <v>0</v>
       </c>
       <c r="J58" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K58" s="2">
         <v>0</v>
@@ -2830,29 +2830,29 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
       <c r="H59" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I59" s="2">
         <v>0</v>
       </c>
       <c r="J59" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K59" s="2">
         <v>0</v>
@@ -2864,29 +2864,29 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I60" s="2">
         <v>0</v>
       </c>
       <c r="J60" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K60" s="2">
         <v>0</v>
@@ -2898,29 +2898,29 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I61" s="2">
         <v>0</v>
       </c>
       <c r="J61" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K61" s="2">
         <v>0</v>
@@ -2932,29 +2932,29 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I62" s="2">
         <v>0</v>
       </c>
       <c r="J62" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K62" s="2">
         <v>0</v>
@@ -2966,29 +2966,29 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I63" s="2">
         <v>0</v>
       </c>
       <c r="J63" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K63" s="2">
         <v>0</v>
@@ -3000,29 +3000,29 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I64" s="2">
         <v>0</v>
       </c>
       <c r="J64" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K64" s="2">
         <v>0</v>
@@ -3034,29 +3034,29 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I65" s="2">
         <v>0</v>
       </c>
       <c r="J65" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K65" s="2">
         <v>0</v>
@@ -3068,29 +3068,29 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I66" s="2">
         <v>0</v>
       </c>
       <c r="J66" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K66" s="2">
         <v>0</v>
@@ -3102,29 +3102,29 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I67" s="2">
         <v>0</v>
       </c>
       <c r="J67" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K67" s="2">
         <v>0</v>
@@ -3136,29 +3136,29 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
       <c r="H68" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I68" s="2">
         <v>0</v>
       </c>
       <c r="J68" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K68" s="2">
         <v>0</v>
@@ -3170,29 +3170,29 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
       <c r="H69" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I69" s="2">
         <v>0</v>
       </c>
       <c r="J69" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K69" s="2">
         <v>0</v>
@@ -3204,29 +3204,29 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I70" s="2">
         <v>0</v>
       </c>
       <c r="J70" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K70" s="2">
         <v>0</v>
@@ -3238,29 +3238,29 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I71" s="2">
         <v>0</v>
       </c>
       <c r="J71" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K71" s="2">
         <v>0</v>
@@ -3272,29 +3272,29 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
       <c r="H72" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I72" s="2">
         <v>0</v>
       </c>
       <c r="J72" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.42883715278</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K72" s="2">
         <v>0</v>
@@ -3306,29 +3306,29 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I73" s="2">
         <v>0</v>
       </c>
       <c r="J73" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K73" s="2">
         <v>0</v>
@@ -3340,29 +3340,29 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
       <c r="H74" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="I74" s="2">
         <v>0</v>
       </c>
       <c r="J74" s="5">
         <f t="shared" ca="1" si="4"/>
-        <v>46316.428837268519</v>
+        <v>46318.509891550922</v>
       </c>
       <c r="K74" s="2">
         <v>0</v>
